--- a/docs/editor/Editor_仕様一覧.xlsx
+++ b/docs/editor/Editor_仕様一覧.xlsx
@@ -20,12 +20,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'入出力定義(REST API)'!$A$4:$F$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'入出力定義(REST API)'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'入出力定義(REST API)'!$A$1:$F$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DB定義(テーブル)'!$A$4:$G$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DB定義(テーブル)'!$A$4:$G$59</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'DB定義(テーブル)'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'DB定義(テーブル)'!$A$1:$G$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DBストアド(sproc)'!$A$4:$D$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'DB定義(テーブル)'!$A$1:$G$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DBストアド(sproc)'!$A$4:$D$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'DBストアド(sproc)'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'DBストアド(sproc)'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'DBストアド(sproc)'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'テスト仕様'!$A$4:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'テスト仕様'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'テスト仕様'!$A$1:$G$14</definedName>
@@ -2045,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2411,66 +2411,66 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>テンプレート台帳</t>
+          <t>ユーザー</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>下書きHTMLファイル</t>
+          <t>ユーザーID</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(260)</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>BIGINT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr"/>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>NULL=下書き無</t>
+          <t>Rep1_運報自動化_Editor_ユーザー</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>テンプレート台帳</t>
+          <t>ユーザー</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>下書きCSSファイル</t>
+          <t>公開ID</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(260)</t>
+          <t>NVARCHAR(64)</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E18" s="9" t="inlineStr"/>
       <c r="F18" s="11" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>API 公開する id</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>テンプレート台帳</t>
+          <t>ユーザー</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>下書き保存者</t>
+          <t>ログインID</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -2479,36 +2479,28 @@
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>テンプレート台帳</t>
+          <t>ユーザー</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>下書き保存日時</t>
+          <t>表示名</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>DATETIME2(3)</t>
+          <t>NVARCHAR(128)</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E20" s="9" t="inlineStr"/>
       <c r="F20" s="11" t="inlineStr"/>
       <c r="G20" s="13" t="inlineStr"/>
     </row>
@@ -2520,24 +2512,20 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>ユーザーID</t>
+          <t>ロール</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>BIGINT IDENTITY</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>NVARCHAR(16)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Rep1_運報自動化_Editor_ユーザー</t>
+          <t>admin / editor / viewer</t>
         </is>
       </c>
     </row>
@@ -2549,22 +2537,22 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>公開ID</t>
+          <t>無効</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(64)</t>
+          <t>BIT</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr"/>
       <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr"/>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>API 公開する id</t>
-        </is>
-      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2574,18 +2562,26 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>ログインID</t>
+          <t>要パスワード変更</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(64)</t>
+          <t>BIT</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>初回ログインで初期化</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
@@ -2595,18 +2591,26 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>表示名</t>
+          <t>PWハッシュ</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(128)</t>
+          <t>VARBINARY(64)</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr"/>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="13" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>PBKDF2 派生鍵。APIに出さない</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2616,22 +2620,22 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ロール</t>
+          <t>PWソルト</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(16)</t>
+          <t>VARBINARY(32)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>admin / editor / viewer</t>
-        </is>
-      </c>
+      <c r="G25" s="8" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -2641,22 +2645,26 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>無効</t>
+          <t>PW反復回数</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>BIT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr"/>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr"/>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr"/>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>PBKDF2 iterations</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2666,26 +2674,22 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>要パスワード変更</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>BIT</t>
+          <t>DATETIME2(3)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>初回ログインで初期化</t>
-        </is>
-      </c>
+          <t>SYSUTCDATETIME()</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
@@ -2695,12 +2699,12 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>PWハッシュ</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>VARBINARY(64)</t>
+          <t>DATETIME2(3)</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr"/>
@@ -2710,154 +2714,134 @@
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>PBKDF2 派生鍵。APIに出さない</t>
-        </is>
-      </c>
+      <c r="G28" s="13" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>ユーザー</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>PWソルト</t>
+          <t>パーツ内部ID</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>VARBINARY(32)</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>BIGINT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Rep1_運報自動化_Editor_パーツカタログ</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>ユーザー</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>PW反復回数</t>
+          <t>パーツID</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>NVARCHAR(64)</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E30" s="9" t="inlineStr"/>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>PBKDF2 iterations</t>
+          <t>data-part-id にも使用</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ユーザー</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>カテゴリ</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>DATETIME2(3)</t>
+          <t>NVARCHAR(64)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>SYSUTCDATETIME()</t>
-        </is>
-      </c>
+      <c r="F31" s="6" t="inlineStr"/>
       <c r="G31" s="8" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>ユーザー</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>大分類</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>DATETIME2(3)</t>
+          <t>NVARCHAR(64)</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E32" s="9" t="inlineStr"/>
       <c r="F32" s="11" t="inlineStr"/>
       <c r="G32" s="13" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>履歴ID</t>
+          <t>中分類</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>BIGINT IDENTITY</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>NVARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>Rep1_運報自動化_Editor_履歴。種別で判別</t>
-        </is>
-      </c>
+      <c r="G33" s="8" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>公開ID</t>
+          <t>小分類</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
@@ -2873,42 +2857,38 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(16)</t>
+          <t>NVARCHAR(128)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>edit / pdf / create / part</t>
-        </is>
-      </c>
+      <c r="G35" s="8" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>テンプレートID</t>
+          <t>説明</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(128)</t>
+          <t>NVARCHAR(512)</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr"/>
@@ -2923,63 +2903,67 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>ログインID</t>
+          <t>使用上の注意</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(64)</t>
+          <t>NVARCHAR(512)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F37" s="6" t="inlineStr"/>
       <c r="G37" s="8" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>発生日時</t>
+          <t>内容HTML</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>DATETIME2(3)</t>
+          <t>NVARCHAR(MAX)</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr"/>
       <c r="E38" s="9" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>SYSUTCDATETIME()</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="inlineStr"/>
+      <c r="F38" s="11" t="inlineStr"/>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>カタログ素材はDB保持</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>概要</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(400)</t>
+          <t>DATETIME2(3)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
@@ -2989,26 +2973,22 @@
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>edit 用</t>
-        </is>
-      </c>
+      <c r="G39" s="8" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>パーツカタログ</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>ファンドコード</t>
+          <t>更新者</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(32)</t>
+          <t>NVARCHAR(64)</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr"/>
@@ -3018,134 +2998,118 @@
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>edit スナップ</t>
-        </is>
-      </c>
+      <c r="G40" s="13" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>スナップHTMLファイル</t>
+          <t>監査ID</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(260)</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>BIGINT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="8" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Rep1_運報自動化_Editor_監査ログ</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>スナップCSSファイル</t>
+          <t>イベント</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(260)</t>
+          <t>NVARCHAR(64)</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E42" s="9" t="inlineStr"/>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="13" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>パーツID</t>
+          <t>結果</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(64)</t>
+          <t>NVARCHAR(8)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>part 用</t>
+          <t>success / failure</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>変更内容</t>
+          <t>実行者</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(512)</t>
+          <t>NVARCHAR(64)</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E44" s="9" t="inlineStr"/>
       <c r="F44" s="11" t="inlineStr"/>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>part 用</t>
-        </is>
-      </c>
+      <c r="G44" s="13" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>委託会社コード</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(32)</t>
+          <t>NVARCHAR(64)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
@@ -3155,26 +3119,22 @@
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>create 用</t>
-        </is>
-      </c>
+      <c r="G45" s="8" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>作成ファンドコード</t>
+          <t>リソースJSON</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(32)</t>
+          <t>NVARCHAR(MAX)</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr"/>
@@ -3186,24 +3146,24 @@
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>create 用</t>
+          <t>テキスト保管</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>基準日</t>
+          <t>詳細JSON</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(8)</t>
+          <t>NVARCHAR(MAX)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr"/>
@@ -3213,26 +3173,22 @@
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>create 用</t>
-        </is>
-      </c>
+      <c r="G47" s="8" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>版種</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(16)</t>
+          <t>NVARCHAR(MAX)</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr"/>
@@ -3242,50 +3198,42 @@
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>create 用</t>
-        </is>
-      </c>
+      <c r="G48" s="13" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>監査ログ</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>元テンプレートID</t>
+          <t>発生日時</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(128)</t>
+          <t>DATETIME2(3)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr"/>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>create 派生元</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>SYSUTCDATETIME()</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>サンプルデータ</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>パーツ内部ID</t>
+          <t>サンプルID</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -3302,86 +3250,90 @@
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Rep1_運報自動化_Editor_パーツカタログ</t>
+          <t>Rep1_運報自動化_Editor_サンプルデータ</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>サンプルデータ</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>パーツID</t>
+          <t>ファンドコード</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(64)</t>
+          <t>NVARCHAR(32)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="6" t="inlineStr"/>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>data-part-id にも使用</t>
-        </is>
-      </c>
+      <c r="G51" s="8" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>サンプルデータ</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>カテゴリ</t>
+          <t>データJSON</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(64)</t>
+          <t>NVARCHAR(MAX)</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr"/>
       <c r="E52" s="9" t="inlineStr"/>
       <c r="F52" s="11" t="inlineStr"/>
-      <c r="G52" s="13" t="inlineStr"/>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>プレビュー context</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>サンプルデータ</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>大分類</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(64)</t>
+          <t>DATETIME2(3)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
-      <c r="E53" s="4" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F53" s="6" t="inlineStr"/>
       <c r="G53" s="8" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>セッション</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>中分類</t>
+          <t>セッションID</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -3389,20 +3341,28 @@
           <t>NVARCHAR(64)</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr"/>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E54" s="9" t="inlineStr"/>
       <c r="F54" s="11" t="inlineStr"/>
-      <c r="G54" s="13" t="inlineStr"/>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>cookie editor.sid</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>セッション</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>小分類</t>
+          <t>ログインID</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -3418,622 +3378,101 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>セッション</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(128)</t>
+          <t>DATETIME2(3)</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr"/>
       <c r="E56" s="9" t="inlineStr"/>
-      <c r="F56" s="11" t="inlineStr"/>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>SYSUTCDATETIME()</t>
+        </is>
+      </c>
       <c r="G56" s="13" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>セッション</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>最終アクセス</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(512)</t>
+          <t>DATETIME2(3)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>SYSUTCDATETIME()</t>
+        </is>
+      </c>
       <c r="G57" s="8" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>セッション</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>使用上の注意</t>
+          <t>有効期限</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>NVARCHAR(512)</t>
+          <t>DATETIME2(3)</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr"/>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E58" s="9" t="inlineStr"/>
       <c r="F58" s="11" t="inlineStr"/>
       <c r="G58" s="13" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>パーツカタログ</t>
+          <t>セッション</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>内容HTML</t>
+          <t>失効</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>NVARCHAR(MAX)</t>
+          <t>BIT</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="6" t="inlineStr"/>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>カタログ素材はDB保持</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>パーツカタログ</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>更新日時</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>DATETIME2(3)</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr"/>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr"/>
-      <c r="G60" s="13" t="inlineStr"/>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>パーツカタログ</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>更新者</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>NVARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr"/>
-      <c r="G61" s="8" t="inlineStr"/>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>監査ID</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>BIGINT IDENTITY</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr"/>
-      <c r="F62" s="11" t="inlineStr"/>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>Rep1_運報自動化_Editor_監査ログ</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>イベント</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>NVARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="6" t="inlineStr"/>
-      <c r="G63" s="8" t="inlineStr"/>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>NVARCHAR(8)</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr"/>
-      <c r="E64" s="9" t="inlineStr"/>
-      <c r="F64" s="11" t="inlineStr"/>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>success / failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>NVARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr"/>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="6" t="inlineStr"/>
-      <c r="G65" s="8" t="inlineStr"/>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>NVARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr"/>
-      <c r="G66" s="13" t="inlineStr"/>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>リソースJSON</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>NVARCHAR(MAX)</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr"/>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr"/>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>テキスト保管</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>詳細JSON</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>NVARCHAR(MAX)</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F68" s="11" t="inlineStr"/>
-      <c r="G68" s="13" t="inlineStr"/>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>NVARCHAR(MAX)</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr"/>
-      <c r="G69" s="8" t="inlineStr"/>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>監査ログ</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>発生日時</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>DATETIME2(3)</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>SYSUTCDATETIME()</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr"/>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>サンプルデータ</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>サンプルID</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>BIGINT IDENTITY</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="6" t="inlineStr"/>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>Rep1_運報自動化_Editor_サンプルデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>サンプルデータ</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>ファンドコード</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>NVARCHAR(32)</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="11" t="inlineStr"/>
-      <c r="G72" s="13" t="inlineStr"/>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>サンプルデータ</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>データJSON</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>NVARCHAR(MAX)</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="6" t="inlineStr"/>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>プレビュー context</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>サンプルデータ</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>更新日時</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>DATETIME2(3)</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr"/>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F74" s="11" t="inlineStr"/>
-      <c r="G74" s="13" t="inlineStr"/>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>セッション</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>セッションID</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>NVARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="6" t="inlineStr"/>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>cookie editor.sid</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>セッション</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>ログインID</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>NVARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr"/>
-      <c r="E76" s="9" t="inlineStr"/>
-      <c r="F76" s="11" t="inlineStr"/>
-      <c r="G76" s="13" t="inlineStr"/>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>セッション</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>作成日時</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>DATETIME2(3)</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>SYSUTCDATETIME()</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr"/>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>セッション</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>最終アクセス</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>DATETIME2(3)</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr"/>
-      <c r="E78" s="9" t="inlineStr"/>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>SYSUTCDATETIME()</t>
-        </is>
-      </c>
-      <c r="G78" s="13" t="inlineStr"/>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>セッション</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>有効期限</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>DATETIME2(3)</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="6" t="inlineStr"/>
-      <c r="G79" s="8" t="inlineStr"/>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>セッション</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>失効</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>BIT</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="11" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G80" s="13" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G80"/>
+  <autoFilter ref="A4:G59"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -4049,7 +3488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4125,12 +3564,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>一覧</t>
+          <t>系列</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>属性フィルタでテンプレート一覧</t>
+          <t>シリーズファンド一覧</t>
         </is>
       </c>
     </row>
@@ -4145,12 +3584,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>取得</t>
+          <t>生成登録</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>1件取得（meta）</t>
+          <t>生成直後に台帳行を draft 作成（冪等）</t>
         </is>
       </c>
     </row>
@@ -4160,17 +3599,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>系列</t>
+          <t>一覧</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>シリーズファンド一覧</t>
+          <t>ユーザー一覧</t>
         </is>
       </c>
     </row>
@@ -4180,17 +3619,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>下書き保存</t>
+          <t>作成</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>オートセーブ（draft 列更新）</t>
+          <t>ユーザー作成</t>
         </is>
       </c>
     </row>
@@ -4200,17 +3639,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>下書き取得</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>下書き本文の索引取得</t>
+          <t>表示名/ロール/無効 更新</t>
         </is>
       </c>
     </row>
@@ -4220,17 +3659,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>確定保存</t>
+          <t>PWリセット</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>状態 published へ確定</t>
+          <t>管理者によるPWリセット（要PW変更）</t>
         </is>
       </c>
     </row>
@@ -4245,12 +3684,12 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>一覧</t>
+          <t>認証情報取得</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>ユーザー一覧</t>
+          <t>ログイン認証用のハッシュ取得</t>
         </is>
       </c>
     </row>
@@ -4265,12 +3704,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>作成</t>
+          <t>PW初期化</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>ユーザー作成</t>
+          <t>初回PW設定</t>
         </is>
       </c>
     </row>
@@ -4280,17 +3719,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>part</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>更新</t>
+          <t>分類候補</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>表示名/ロール/無効 更新</t>
+          <t>分類ドロップダウン候補（カテゴリ/大/中/小）</t>
         </is>
       </c>
     </row>
@@ -4300,17 +3739,17 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>part</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>PWリセット</t>
+          <t>一覧</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>管理者によるPWリセット（要PW変更）</t>
+          <t>分類フィルタでパーツカタログ一覧</t>
         </is>
       </c>
     </row>
@@ -4320,17 +3759,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>認証情報取得</t>
+          <t>取得</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>ログイン認証用のハッシュ取得</t>
+          <t>ファンド別サンプルデータ取得</t>
         </is>
       </c>
     </row>
@@ -4340,17 +3779,17 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>PW初期化</t>
+          <t>登録</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>初回PW設定</t>
+          <t>ファンド別サンプルデータの upsert</t>
         </is>
       </c>
     </row>
@@ -4360,17 +3799,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>session</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>一覧</t>
+          <t>作成</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>種別別の履歴一覧</t>
+          <t>セッション発行</t>
         </is>
       </c>
     </row>
@@ -4380,17 +3819,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>session</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>一覧</t>
+          <t>取得</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>パーツカタログ一覧</t>
+          <t>セッション検証（期限/失効）＋ユーザー結合</t>
         </is>
       </c>
     </row>
@@ -4400,17 +3839,17 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>session</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>取得</t>
+          <t>失効</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>ファンド別サンプルデータ取得</t>
+          <t>ログアウトで失効</t>
         </is>
       </c>
     </row>
@@ -4420,17 +3859,17 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>session</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>作成</t>
+          <t>登録</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>セッション発行</t>
+          <t>監査イベント記録（logger.ts 連携）</t>
         </is>
       </c>
     </row>
@@ -4440,62 +3879,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>session</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>取得</t>
+          <t>検索</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>セッション検証（期限/失効）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>session</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>失効</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>ログアウトで失効</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>audit</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>記録</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>監査イベント記録（logger.ts 連携）</t>
+          <t>イベント絞込で最新500件取得</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D24"/>
+  <autoFilter ref="A4:D22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
